--- a/jogos_2025-06-04.xlsx
+++ b/jogos_2025-06-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -238,10 +184,34 @@
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['-1', '-1', '-1']</t>
+  </si>
+  <si>
+    <t>['43', '45+1']</t>
+  </si>
+  <si>
+    <t>['45', '72', '77']</t>
+  </si>
+  <si>
+    <t>['-1', '-1']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['21', '40', '55', '69', '89']</t>
+  </si>
+  <si>
+    <t>['57', '87']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -605,10 +575,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,85 +693,31 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45812</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -810,16 +726,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L2">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="M2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="O2">
         <v>1.83</v>
@@ -831,165 +747,111 @@
         <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V2">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z2">
+        <v>1.33</v>
+      </c>
+      <c r="AA2">
+        <v>3.2</v>
+      </c>
+      <c r="AB2">
+        <v>1.97</v>
+      </c>
+      <c r="AC2">
+        <v>1.72</v>
+      </c>
+      <c r="AD2">
+        <v>3.5</v>
+      </c>
+      <c r="AE2">
         <v>1.22</v>
       </c>
-      <c r="AA2">
-        <v>3.4</v>
-      </c>
-      <c r="AB2">
-        <v>1.8</v>
-      </c>
-      <c r="AC2">
-        <v>1.83</v>
-      </c>
-      <c r="AD2">
-        <v>3.2</v>
-      </c>
-      <c r="AE2">
-        <v>1.28</v>
-      </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="AK2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL2">
-        <v>1.3</v>
-      </c>
-      <c r="AM2">
-        <v>1.28</v>
-      </c>
-      <c r="AN2">
-        <v>1.5</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.27</v>
-      </c>
-      <c r="AQ2">
-        <v>1.5</v>
-      </c>
-      <c r="AR2">
-        <v>2.07</v>
-      </c>
-      <c r="AS2">
-        <v>2.31</v>
-      </c>
-      <c r="AT2">
-        <v>2.92</v>
-      </c>
-      <c r="AU2">
-        <v>3.27</v>
-      </c>
-      <c r="AV2">
-        <v>2.42</v>
-      </c>
-      <c r="AW2">
-        <v>1.91</v>
-      </c>
-      <c r="AX2">
-        <v>1.57</v>
-      </c>
-      <c r="AY2">
-        <v>1.35</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.83</v>
-      </c>
-      <c r="BC2">
-        <v>2.1</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>62</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45812.54166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45812</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L3">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O3">
         <v>2.1</v>
@@ -1001,165 +863,111 @@
         <v>1.67</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="W3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AA3">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB3">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>1.75</v>
+        <v>2.42</v>
       </c>
       <c r="AE3">
-        <v>1.93</v>
+        <v>1.51</v>
       </c>
       <c r="AF3">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AG3">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH3">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="AI3">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="AJ3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="AK3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL3">
-        <v>1.17</v>
-      </c>
-      <c r="AM3">
-        <v>1.22</v>
-      </c>
-      <c r="AN3">
-        <v>1.42</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.1</v>
-      </c>
-      <c r="BC3">
-        <v>1.67</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>63</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45812.83333333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45812</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="M4">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1171,144 +979,90 @@
         <v>3.4</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T4">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
+        <v>1.34</v>
+      </c>
+      <c r="V4">
+        <v>8.25</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>7.3</v>
+      </c>
+      <c r="Z4">
         <v>1.36</v>
       </c>
-      <c r="V4">
-        <v>7.5</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>8</v>
-      </c>
-      <c r="Z4">
-        <v>1.32</v>
-      </c>
       <c r="AA4">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AC4">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AD4">
         <v>4.2</v>
       </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH4">
         <v>7.8</v>
       </c>
       <c r="AI4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AK4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL4">
-        <v>1.29</v>
-      </c>
-      <c r="AM4">
-        <v>1.26</v>
-      </c>
-      <c r="AN4">
-        <v>2.38</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4">
-        <v>1.42</v>
-      </c>
-      <c r="AR4">
-        <v>1.67</v>
-      </c>
-      <c r="AS4">
-        <v>2.05</v>
-      </c>
-      <c r="AT4">
-        <v>2.63</v>
-      </c>
-      <c r="AU4">
-        <v>3.6</v>
-      </c>
-      <c r="AV4">
-        <v>2.3</v>
-      </c>
-      <c r="AW4">
-        <v>2.1</v>
-      </c>
-      <c r="AX4">
-        <v>1.65</v>
-      </c>
-      <c r="AY4">
-        <v>1.44</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.44</v>
-      </c>
-      <c r="BC4">
-        <v>3.4</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>64</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45812.83333333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45812</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1320,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L5">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="M5">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N5">
-        <v>2.96</v>
+        <v>3.33</v>
       </c>
       <c r="O5">
         <v>1.53</v>
@@ -1341,16 +1095,16 @@
         <v>2.38</v>
       </c>
       <c r="R5">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="U5">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="V5">
         <v>3.6</v>
@@ -1365,141 +1119,87 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AB5">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC5">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE5">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AF5">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AG5">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AH5">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="AI5">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AJ5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL5">
-        <v>1.15</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1.7</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.53</v>
-      </c>
-      <c r="BC5">
-        <v>2.38</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>61</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45812.875</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45812</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="L6">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="M6">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N6">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
         <v>1.73</v>
@@ -1511,120 +1211,66 @@
         <v>2.05</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="T6">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
         <v>1.55</v>
       </c>
       <c r="V6">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="Z6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA6">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AD6">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="AE6">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AF6">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH6">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AI6">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="AK6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL6">
-        <v>1.27</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1.42</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>1.9</v>
-      </c>
-      <c r="AS6">
-        <v>2</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>2.01</v>
-      </c>
-      <c r="AX6">
-        <v>1.8</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.73</v>
-      </c>
-      <c r="BC6">
-        <v>2.05</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>65</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45812.875</v>
       </c>
     </row>

--- a/jogos_2025-06-04.xlsx
+++ b/jogos_2025-06-04.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>3.07</v>
       </c>
       <c r="T5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.07</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45812.875</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.25</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45812.875</v>
